--- a/Level3_LowerBody_Day2_V1_SubLevel2_Micro_Cycles-2.xlsx
+++ b/Level3_LowerBody_Day2_V1_SubLevel2_Micro_Cycles-2.xlsx
@@ -554,10 +554,10 @@
       <c r="Y1" s="4" t="n"/>
       <c r="Z1" s="4" t="n"/>
     </row>
-    <row r="2" ht="25.5" customHeight="1" s="27">
+    <row r="2" ht="66" customHeight="1" s="27">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>One PRESCRIPTION per exercise — a working range that runs from below the standard up to the standard. Own the standard and you are ready to attempt the test. ○ = working grade, 0 = Foundation (non-gating), 2·3 = carries in both Sub-Level 2 and 3, 1·2 = carries in both Sub-Level 1 and 2. Self-paced. Every cell is a per-set prescription.</t>
+          <t>Self-paced. Train inside the PRESCRIPTION; its top is the STANDARD. One set at the standard = that exercise is passed. Clear a slot by passing 2 different exercises from its list (1 if it lists only one) — ○ 0 Foundations count, warm-ups/prep/activation/rotator don't. Clear every slot to move to the next phase. PICK 1 = choose one, PICK 2 = choose two. Every cell is a per-set prescription. Weighted rows: up to 1–2 warm-up sets below the range, then at least 1 set inside it. ○ = working grade · 0 = Foundation · 2·3 = carries in both Sub-Level 2 and 3, 1·2 = carries in both Sub-Level 1 and 2. Version 1 and Version 2 alternate session to session — the phase clears once every slot of BOTH versions is cleared. The A · CORE category and C · JUMPING or C · FLEXIBILITY are your pick each session — clear the slots of BOTH Jumping and Flexibility to finish the phase.</t>
         </is>
       </c>
       <c r="G2" s="4" t="n"/>
